--- a/maestros/Intervenciones_P2R_Ondupet.xlsx
+++ b/maestros/Intervenciones_P2R_Ondupet.xlsx
@@ -96,7 +96,7 @@
     <t xml:space="preserve">P2R-01 · Gestión de la demanda</t>
   </si>
   <si>
-    <t xml:space="preserve">HT-P2R-01, HT-P2R-02</t>
+    <t xml:space="preserve">HT-P2R-01</t>
   </si>
   <si>
     <t xml:space="preserve">Negocio</t>
